--- a/outputs/evaluation/architecture/design/v3/CF_M05/run_1/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v3/CF_M05/run_1/CF_M05_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6098</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6176</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7368</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9341</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5714</v>
       </c>
       <c r="D4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.782</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7503</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_24</t>
@@ -1233,7 +1245,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M05_AU22</t>
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.762</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_08', 'AU_09', 'AU_10', 'AU_11', 'AU_12']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_21</t>
@@ -1315,7 +1323,6 @@
           <t>leader service, portal service, access control service, communication log service, scheduler service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M05_AU04, CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M05_AU23</t>
@@ -1385,14 +1391,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Leader Microservice</t>
@@ -1418,13 +1421,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M05_AU01</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1445,7 +1446,6 @@
       <c r="D5" t="n">
         <v>0.8048</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1466,7 +1466,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_23</t>
@@ -1477,7 +1476,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1496,7 +1494,6 @@
           <t>CF_M05_AU14, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M05_AU34</t>
@@ -1527,7 +1524,6 @@
       <c r="D6" t="n">
         <v>0.8109</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1548,7 +1544,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_20</t>
@@ -1559,7 +1554,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1578,7 +1572,6 @@
           <t>CF_M05_AU06, CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M05_AU24</t>
@@ -1634,13 +1627,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Client(Frontend)</t>
@@ -1666,13 +1657,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,13 +1707,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Contract Layer (DTO/Mappers)</t>
@@ -1749,13 +1736,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M05_AU20</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1796,14 +1781,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Access Control Microservice</t>
@@ -1828,13 +1810,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M05_AU03</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1880,13 +1860,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
@@ -1911,13 +1889,11 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1958,14 +1934,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Portal Microservice</t>
@@ -1992,13 +1965,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2039,14 +2010,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Scheduler Microservice</t>
@@ -2075,13 +2043,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M05_AU05</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2122,14 +2088,11 @@
           <t>58</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Communication Log Microservice</t>
@@ -2158,13 +2121,11 @@
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M05_AU04</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2210,13 +2171,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Presentation Layer (Controllers)</t>
@@ -2242,13 +2201,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M05_AU17</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2294,13 +2251,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Data access layer (Repositories)</t>
@@ -2324,13 +2279,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M05_AU21</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2376,13 +2329,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Domain Layer (Models)</t>
@@ -2407,13 +2358,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M05_AU19</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2459,13 +2408,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Business Logic Layer (Services)</t>
@@ -2489,13 +2436,11 @@
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M05_AU18</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2541,13 +2486,11 @@
           <t>['AU_18']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Kubernetes</t>
@@ -2574,13 +2517,11 @@
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M05_AU35</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2626,13 +2567,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
@@ -2654,14 +2593,11 @@
       <c r="P19" t="n">
         <v>68.69</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M05_P04</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2707,13 +2643,11 @@
           <t>['AU_23', 'AU_24']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2738,13 +2672,11 @@
           <t>CF_M05_AU34</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M05_AU31</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2790,13 +2722,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
@@ -2822,13 +2752,11 @@
           <t>CF_M05_P05</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M05_AU07</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2874,13 +2802,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Spring Boot</t>
@@ -2906,13 +2832,11 @@
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M05_AU29</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2958,13 +2882,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>MVVM</t>
@@ -2984,14 +2906,11 @@
       <c r="P23" t="n">
         <v>62</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3037,13 +2956,11 @@
           <t>['AU_01']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Angular</t>
@@ -3067,13 +2984,11 @@
           <t>CF_M05_AU06</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M05_AU30</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3114,14 +3029,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -3140,14 +3052,11 @@
       <c r="P25" t="n">
         <v>56</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M05_P01</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3188,14 +3097,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3216,7 +3122,6 @@
       <c r="P26" t="n">
         <v>61</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Design Pattern</t>
@@ -3227,7 +3132,6 @@
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3301,7 +3205,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Data format used for message exchange.</t>
@@ -3337,7 +3240,6 @@
           <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Cloud provider for the project.</t>
@@ -3368,7 +3270,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>portal service, presentation layer</t>
@@ -3465,7 +3366,6 @@
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>SonarQube is a
@@ -3504,7 +3404,6 @@
           <t>Grafana</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
@@ -3540,7 +3439,6 @@
           <t>Amazon RDS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
@@ -3577,7 +3475,6 @@
           <t>Ordering</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3614,7 +3511,6 @@
           <t>GSB</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>These two microservices are responsible for
@@ -3651,7 +3547,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
@@ -3689,7 +3584,6 @@
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
@@ -3727,7 +3621,6 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
@@ -3765,7 +3658,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
@@ -3798,7 +3690,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>presentation layer (controllers), data access layer (repositories)</t>
@@ -3814,7 +3705,6 @@
           <t>AU_24</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0.7419</v>
       </c>
@@ -3830,7 +3720,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>data access layer (repositories), database</t>
@@ -3866,7 +3755,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>viewmodel, view, model</t>
@@ -3907,7 +3795,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
@@ -3944,7 +3831,6 @@
           <t>Docker</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
@@ -3980,7 +3866,6 @@
           <t>Cloud Architecture</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The application applies a cloud architecture . That is, the application is designed,
@@ -4017,7 +3902,6 @@
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
